--- a/Mapping & Audit Data/Migration Audit Sheet .xlsx
+++ b/Mapping & Audit Data/Migration Audit Sheet .xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Object (Target API Name)</t>
   </si>
@@ -62,33 +62,6 @@
   </si>
   <si>
     <t>OpportunityTeamMember</t>
-  </si>
-  <si>
-    <t>Account_Role__c</t>
-  </si>
-  <si>
-    <t>New Object</t>
-  </si>
-  <si>
-    <t>Builder_Metrics__c</t>
-  </si>
-  <si>
-    <t>docebo_Course_Enrollment__c</t>
-  </si>
-  <si>
-    <t>docebo_LP_Enrollment__c</t>
-  </si>
-  <si>
-    <t>Opportunity_Dealers__c</t>
-  </si>
-  <si>
-    <t>Quote_Request__c</t>
-  </si>
-  <si>
-    <t>Request_Line_Item__c</t>
-  </si>
-  <si>
-    <t>Survey__c</t>
   </si>
 </sst>
 </file>
@@ -121,7 +94,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,32 +107,21 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC4125"/>
-        <bgColor rgb="FFCC4125"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF3D444D"/>
-      </left>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -168,14 +130,13 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -441,10 +402,6 @@
       <c r="E2" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F2" s="5">
-        <f t="shared" ref="F2:F11" si="1">MINUS(B2,D2)</f>
-        <v>-371728</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -462,10 +419,6 @@
       <c r="E3" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F3" s="5">
-        <f t="shared" si="1"/>
-        <v>404771</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -483,10 +436,6 @@
       <c r="E4" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F4" s="5">
-        <f t="shared" si="1"/>
-        <v>-264</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
@@ -504,10 +453,6 @@
       <c r="E5" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F5" s="5">
-        <f t="shared" si="1"/>
-        <v>11031</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
@@ -525,10 +470,6 @@
       <c r="E6" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>-529</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
@@ -546,10 +487,6 @@
       <c r="E7" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F7" s="5">
-        <f t="shared" si="1"/>
-        <v>4823470</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
@@ -567,10 +504,6 @@
       <c r="E8" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F8" s="5">
-        <f t="shared" si="1"/>
-        <v>70550</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
@@ -588,10 +521,6 @@
       <c r="E9" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F9" s="5">
-        <f t="shared" si="1"/>
-        <v>-13620472</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -609,10 +538,6 @@
       <c r="E10" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F10" s="5">
-        <f t="shared" si="1"/>
-        <v>21542</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
@@ -630,146 +555,78 @@
       <c r="E11" s="4">
         <v>46238.0</v>
       </c>
-      <c r="F11" s="5">
-        <f t="shared" si="1"/>
-        <v>491410</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="6">
-        <v>844.0</v>
-      </c>
-      <c r="C12" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="C13" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="6">
-        <v>102542.0</v>
-      </c>
-      <c r="C14" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="6">
-        <v>7335.0</v>
-      </c>
-      <c r="C15" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="6">
-        <v>64303.0</v>
-      </c>
-      <c r="C16" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="6">
-        <v>5236.0</v>
-      </c>
-      <c r="C17" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="6">
-        <v>5451.0</v>
-      </c>
-      <c r="C18" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="6">
-        <v>47964.0</v>
-      </c>
-      <c r="C19" s="7">
-        <v>46238.0</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
